--- a/SECURITY/immigration_personnel_population.xlsx
+++ b/SECURITY/immigration_personnel_population.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="6">
-  <si>
-    <t>lga_id</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="27">
+  <si>
+    <t>lga</t>
   </si>
   <si>
     <t>year</t>
@@ -26,6 +26,69 @@
   </si>
   <si>
     <t>population</t>
+  </si>
+  <si>
+    <t>AGUATA</t>
+  </si>
+  <si>
+    <t>ANAMBRA EAST</t>
+  </si>
+  <si>
+    <t>ANAMBRA WEST</t>
+  </si>
+  <si>
+    <t>ANAOCHA</t>
+  </si>
+  <si>
+    <t>AWKA NORTH</t>
+  </si>
+  <si>
+    <t>AWKA SOUTH</t>
+  </si>
+  <si>
+    <t>AYAMELUM</t>
+  </si>
+  <si>
+    <t>DUNUKOFIA</t>
+  </si>
+  <si>
+    <t>EKWUSIGO</t>
+  </si>
+  <si>
+    <t>IDEMILI NORTH</t>
+  </si>
+  <si>
+    <t>IDEMILI SOUTH</t>
+  </si>
+  <si>
+    <t>IHIALA</t>
+  </si>
+  <si>
+    <t>NJIKOKA</t>
+  </si>
+  <si>
+    <t>NNEWI NORTH</t>
+  </si>
+  <si>
+    <t>NNEWI SOUTH</t>
+  </si>
+  <si>
+    <t>OGBARU</t>
+  </si>
+  <si>
+    <t>ONITSHA NORTH</t>
+  </si>
+  <si>
+    <t>ONITSHA SOUTH</t>
+  </si>
+  <si>
+    <t>ORUMBA NORTH</t>
+  </si>
+  <si>
+    <t>ORUMBA SOUTH</t>
+  </si>
+  <si>
+    <t>OYI</t>
   </si>
   <si>
     <t>MALE</t>
@@ -407,1764 +470,1764 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2">
-        <v>13</v>
+      <c r="A2" t="s">
+        <v>4</v>
       </c>
       <c r="B2">
         <v>2019</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D2">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3">
-        <v>13</v>
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
       <c r="B3">
         <v>2019</v>
       </c>
       <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>18</v>
-      </c>
       <c r="B4">
         <v>2019</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D4">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5">
-        <v>18</v>
+      <c r="A5" t="s">
+        <v>5</v>
       </c>
       <c r="B5">
         <v>2019</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6">
-        <v>2</v>
+      <c r="A6" t="s">
+        <v>6</v>
       </c>
       <c r="B6">
         <v>2019</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7">
-        <v>2</v>
+      <c r="A7" t="s">
+        <v>6</v>
       </c>
       <c r="B7">
         <v>2019</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8">
-        <v>9</v>
+      <c r="A8" t="s">
+        <v>7</v>
       </c>
       <c r="B8">
         <v>2019</v>
       </c>
       <c r="C8" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D8">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9">
-        <v>9</v>
+      <c r="A9" t="s">
+        <v>7</v>
       </c>
       <c r="B9">
         <v>2019</v>
       </c>
       <c r="C9" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10">
-        <v>15</v>
+      <c r="A10" t="s">
+        <v>8</v>
       </c>
       <c r="B10">
         <v>2019</v>
       </c>
       <c r="C10" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D10">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11">
-        <v>15</v>
+      <c r="A11" t="s">
+        <v>8</v>
       </c>
       <c r="B11">
         <v>2019</v>
       </c>
       <c r="C11" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12">
-        <v>20</v>
+      <c r="A12" t="s">
+        <v>9</v>
       </c>
       <c r="B12">
         <v>2019</v>
       </c>
       <c r="C12" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13">
-        <v>20</v>
+      <c r="A13" t="s">
+        <v>9</v>
       </c>
       <c r="B13">
         <v>2019</v>
       </c>
       <c r="C13" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14">
-        <v>6</v>
+      <c r="A14" t="s">
+        <v>10</v>
       </c>
       <c r="B14">
         <v>2019</v>
       </c>
       <c r="C14" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15">
-        <v>6</v>
+      <c r="A15" t="s">
+        <v>10</v>
       </c>
       <c r="B15">
         <v>2019</v>
       </c>
       <c r="C15" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16">
-        <v>12</v>
+      <c r="A16" t="s">
+        <v>11</v>
       </c>
       <c r="B16">
         <v>2019</v>
       </c>
       <c r="C16" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17">
-        <v>12</v>
+      <c r="A17" t="s">
+        <v>11</v>
       </c>
       <c r="B17">
         <v>2019</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D17">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="s">
+        <v>12</v>
       </c>
       <c r="B18">
         <v>2019</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D18">
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19">
-        <v>17</v>
+      <c r="A19" t="s">
+        <v>12</v>
       </c>
       <c r="B19">
         <v>2019</v>
       </c>
       <c r="C19" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20">
-        <v>8</v>
+      <c r="A20" t="s">
+        <v>13</v>
       </c>
       <c r="B20">
         <v>2019</v>
       </c>
       <c r="C20" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21">
-        <v>8</v>
+      <c r="A21" t="s">
+        <v>13</v>
       </c>
       <c r="B21">
         <v>2019</v>
       </c>
       <c r="C21" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D21">
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22">
-        <v>3</v>
+      <c r="A22" t="s">
+        <v>14</v>
       </c>
       <c r="B22">
         <v>2019</v>
       </c>
       <c r="C22" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D22">
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23">
-        <v>3</v>
+      <c r="A23" t="s">
+        <v>14</v>
       </c>
       <c r="B23">
         <v>2019</v>
       </c>
       <c r="C23" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D23">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24">
-        <v>16</v>
+      <c r="A24" t="s">
+        <v>15</v>
       </c>
       <c r="B24">
         <v>2019</v>
       </c>
       <c r="C24" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D24">
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25">
-        <v>16</v>
+      <c r="A25" t="s">
+        <v>15</v>
       </c>
       <c r="B25">
         <v>2019</v>
       </c>
       <c r="C25" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D25">
         <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26">
-        <v>11</v>
+      <c r="A26" t="s">
+        <v>16</v>
       </c>
       <c r="B26">
         <v>2019</v>
       </c>
       <c r="C26" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D26">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27">
-        <v>11</v>
+      <c r="A27" t="s">
+        <v>16</v>
       </c>
       <c r="B27">
         <v>2019</v>
       </c>
       <c r="C27" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28">
-        <v>10</v>
+      <c r="A28" t="s">
+        <v>17</v>
       </c>
       <c r="B28">
         <v>2019</v>
       </c>
       <c r="C28" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D28">
         <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29">
-        <v>10</v>
+      <c r="A29" t="s">
+        <v>17</v>
       </c>
       <c r="B29">
         <v>2019</v>
       </c>
       <c r="C29" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30">
-        <v>4</v>
+      <c r="A30" t="s">
+        <v>18</v>
       </c>
       <c r="B30">
         <v>2019</v>
       </c>
       <c r="C30" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31">
-        <v>4</v>
+      <c r="A31" t="s">
+        <v>18</v>
       </c>
       <c r="B31">
         <v>2019</v>
       </c>
       <c r="C31" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D31">
         <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32">
+      <c r="A32" t="s">
         <v>19</v>
       </c>
       <c r="B32">
         <v>2019</v>
       </c>
       <c r="C32" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33">
+      <c r="A33" t="s">
         <v>19</v>
       </c>
       <c r="B33">
         <v>2019</v>
       </c>
       <c r="C33" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D33">
         <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34">
-        <v>14</v>
+      <c r="A34" t="s">
+        <v>20</v>
       </c>
       <c r="B34">
         <v>2019</v>
       </c>
       <c r="C34" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D34">
         <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35">
-        <v>14</v>
+      <c r="A35" t="s">
+        <v>20</v>
       </c>
       <c r="B35">
         <v>2019</v>
       </c>
       <c r="C35" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D35">
         <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36">
-        <v>1</v>
+      <c r="A36" t="s">
+        <v>21</v>
       </c>
       <c r="B36">
         <v>2019</v>
       </c>
       <c r="C36" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D36">
         <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37">
-        <v>1</v>
+      <c r="A37" t="s">
+        <v>21</v>
       </c>
       <c r="B37">
         <v>2019</v>
       </c>
       <c r="C37" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D37">
         <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38">
-        <v>7</v>
+      <c r="A38" t="s">
+        <v>22</v>
       </c>
       <c r="B38">
         <v>2019</v>
       </c>
       <c r="C38" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39">
-        <v>7</v>
+      <c r="A39" t="s">
+        <v>22</v>
       </c>
       <c r="B39">
         <v>2019</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D39">
         <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40">
-        <v>21</v>
+      <c r="A40" t="s">
+        <v>23</v>
       </c>
       <c r="B40">
         <v>2019</v>
       </c>
       <c r="C40" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D40">
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41">
-        <v>21</v>
+      <c r="A41" t="s">
+        <v>23</v>
       </c>
       <c r="B41">
         <v>2019</v>
       </c>
       <c r="C41" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D41">
         <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42">
-        <v>5</v>
+      <c r="A42" t="s">
+        <v>24</v>
       </c>
       <c r="B42">
         <v>2019</v>
       </c>
       <c r="C42" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D42">
         <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43">
-        <v>5</v>
+      <c r="A43" t="s">
+        <v>24</v>
       </c>
       <c r="B43">
         <v>2019</v>
       </c>
       <c r="C43" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D43">
         <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44">
-        <v>13</v>
+      <c r="A44" t="s">
+        <v>4</v>
       </c>
       <c r="B44">
         <v>2020</v>
       </c>
       <c r="C44" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D44">
         <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45">
-        <v>13</v>
+      <c r="A45" t="s">
+        <v>4</v>
       </c>
       <c r="B45">
         <v>2020</v>
       </c>
       <c r="C45" t="s">
+        <v>26</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
         <v>5</v>
       </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46">
-        <v>18</v>
-      </c>
       <c r="B46">
         <v>2020</v>
       </c>
       <c r="C46" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D46">
         <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47">
-        <v>18</v>
+      <c r="A47" t="s">
+        <v>5</v>
       </c>
       <c r="B47">
         <v>2020</v>
       </c>
       <c r="C47" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48">
-        <v>2</v>
+      <c r="A48" t="s">
+        <v>6</v>
       </c>
       <c r="B48">
         <v>2020</v>
       </c>
       <c r="C48" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D48">
         <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49">
-        <v>2</v>
+      <c r="A49" t="s">
+        <v>6</v>
       </c>
       <c r="B49">
         <v>2020</v>
       </c>
       <c r="C49" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50">
-        <v>9</v>
+      <c r="A50" t="s">
+        <v>7</v>
       </c>
       <c r="B50">
         <v>2020</v>
       </c>
       <c r="C50" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D50">
         <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51">
-        <v>9</v>
+      <c r="A51" t="s">
+        <v>7</v>
       </c>
       <c r="B51">
         <v>2020</v>
       </c>
       <c r="C51" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52">
-        <v>15</v>
+      <c r="A52" t="s">
+        <v>8</v>
       </c>
       <c r="B52">
         <v>2020</v>
       </c>
       <c r="C52" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D52">
         <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53">
-        <v>15</v>
+      <c r="A53" t="s">
+        <v>8</v>
       </c>
       <c r="B53">
         <v>2020</v>
       </c>
       <c r="C53" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D53">
         <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54">
-        <v>20</v>
+      <c r="A54" t="s">
+        <v>9</v>
       </c>
       <c r="B54">
         <v>2020</v>
       </c>
       <c r="C54" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D54">
         <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55">
-        <v>20</v>
+      <c r="A55" t="s">
+        <v>9</v>
       </c>
       <c r="B55">
         <v>2020</v>
       </c>
       <c r="C55" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D55">
         <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56">
-        <v>6</v>
+      <c r="A56" t="s">
+        <v>10</v>
       </c>
       <c r="B56">
         <v>2020</v>
       </c>
       <c r="C56" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D56">
         <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57">
-        <v>6</v>
+      <c r="A57" t="s">
+        <v>10</v>
       </c>
       <c r="B57">
         <v>2020</v>
       </c>
       <c r="C57" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D57">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58">
-        <v>12</v>
+      <c r="A58" t="s">
+        <v>11</v>
       </c>
       <c r="B58">
         <v>2020</v>
       </c>
       <c r="C58" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D58">
         <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59">
+      <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59">
+        <v>2020</v>
+      </c>
+      <c r="C59" t="s">
+        <v>26</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
         <v>12</v>
       </c>
-      <c r="B59">
-        <v>2020</v>
-      </c>
-      <c r="C59" t="s">
-        <v>5</v>
-      </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60">
-        <v>17</v>
-      </c>
       <c r="B60">
         <v>2020</v>
       </c>
       <c r="C60" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D60">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61">
-        <v>17</v>
+      <c r="A61" t="s">
+        <v>12</v>
       </c>
       <c r="B61">
         <v>2020</v>
       </c>
       <c r="C61" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D61">
         <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62">
-        <v>8</v>
+      <c r="A62" t="s">
+        <v>13</v>
       </c>
       <c r="B62">
         <v>2020</v>
       </c>
       <c r="C62" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D62">
         <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63">
-        <v>8</v>
+      <c r="A63" t="s">
+        <v>13</v>
       </c>
       <c r="B63">
         <v>2020</v>
       </c>
       <c r="C63" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D63">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64">
-        <v>3</v>
+      <c r="A64" t="s">
+        <v>14</v>
       </c>
       <c r="B64">
         <v>2020</v>
       </c>
       <c r="C64" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D64">
         <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65">
-        <v>3</v>
+      <c r="A65" t="s">
+        <v>14</v>
       </c>
       <c r="B65">
         <v>2020</v>
       </c>
       <c r="C65" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D65">
         <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66">
+        <v>2020</v>
+      </c>
+      <c r="C66" t="s">
+        <v>25</v>
+      </c>
+      <c r="D66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67">
+        <v>2020</v>
+      </c>
+      <c r="C67" t="s">
+        <v>26</v>
+      </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
         <v>16</v>
       </c>
-      <c r="B66">
-        <v>2020</v>
-      </c>
-      <c r="C66" t="s">
-        <v>4</v>
-      </c>
-      <c r="D66">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67">
+      <c r="B68">
+        <v>2020</v>
+      </c>
+      <c r="C68" t="s">
+        <v>25</v>
+      </c>
+      <c r="D68">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
         <v>16</v>
       </c>
-      <c r="B67">
-        <v>2020</v>
-      </c>
-      <c r="C67" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68">
-        <v>11</v>
-      </c>
-      <c r="B68">
-        <v>2020</v>
-      </c>
-      <c r="C68" t="s">
-        <v>4</v>
-      </c>
-      <c r="D68">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69">
-        <v>11</v>
-      </c>
       <c r="B69">
         <v>2020</v>
       </c>
       <c r="C69" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D69">
         <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70">
-        <v>10</v>
+      <c r="A70" t="s">
+        <v>17</v>
       </c>
       <c r="B70">
         <v>2020</v>
       </c>
       <c r="C70" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D70">
         <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71">
-        <v>10</v>
+      <c r="A71" t="s">
+        <v>17</v>
       </c>
       <c r="B71">
         <v>2020</v>
       </c>
       <c r="C71" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D71">
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72">
-        <v>4</v>
+      <c r="A72" t="s">
+        <v>18</v>
       </c>
       <c r="B72">
         <v>2020</v>
       </c>
       <c r="C72" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D72">
         <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73">
-        <v>4</v>
+      <c r="A73" t="s">
+        <v>18</v>
       </c>
       <c r="B73">
         <v>2020</v>
       </c>
       <c r="C73" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D73">
         <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74">
+      <c r="A74" t="s">
         <v>19</v>
       </c>
       <c r="B74">
         <v>2020</v>
       </c>
       <c r="C74" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D74">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75">
+      <c r="A75" t="s">
         <v>19</v>
       </c>
       <c r="B75">
         <v>2020</v>
       </c>
       <c r="C75" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D75">
         <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76">
-        <v>14</v>
+      <c r="A76" t="s">
+        <v>20</v>
       </c>
       <c r="B76">
         <v>2020</v>
       </c>
       <c r="C76" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D76">
         <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77">
-        <v>14</v>
+      <c r="A77" t="s">
+        <v>20</v>
       </c>
       <c r="B77">
         <v>2020</v>
       </c>
       <c r="C77" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D77">
         <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78">
-        <v>1</v>
+      <c r="A78" t="s">
+        <v>21</v>
       </c>
       <c r="B78">
         <v>2020</v>
       </c>
       <c r="C78" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D78">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79">
-        <v>1</v>
+      <c r="A79" t="s">
+        <v>21</v>
       </c>
       <c r="B79">
         <v>2020</v>
       </c>
       <c r="C79" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80">
-        <v>7</v>
+      <c r="A80" t="s">
+        <v>22</v>
       </c>
       <c r="B80">
         <v>2020</v>
       </c>
       <c r="C80" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D80">
         <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81">
-        <v>7</v>
+      <c r="A81" t="s">
+        <v>22</v>
       </c>
       <c r="B81">
         <v>2020</v>
       </c>
       <c r="C81" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D81">
         <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82">
-        <v>21</v>
+      <c r="A82" t="s">
+        <v>23</v>
       </c>
       <c r="B82">
         <v>2020</v>
       </c>
       <c r="C82" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D82">
         <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83">
-        <v>21</v>
+      <c r="A83" t="s">
+        <v>23</v>
       </c>
       <c r="B83">
         <v>2020</v>
       </c>
       <c r="C83" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D83">
         <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84">
-        <v>5</v>
+      <c r="A84" t="s">
+        <v>24</v>
       </c>
       <c r="B84">
         <v>2020</v>
       </c>
       <c r="C84" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D84">
         <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85">
-        <v>5</v>
+      <c r="A85" t="s">
+        <v>24</v>
       </c>
       <c r="B85">
         <v>2020</v>
       </c>
       <c r="C85" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D85">
         <v>4</v>
       </c>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86">
-        <v>13</v>
+      <c r="A86" t="s">
+        <v>4</v>
       </c>
       <c r="B86">
         <v>2021</v>
       </c>
       <c r="C86" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D86">
         <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:4">
-      <c r="A87">
-        <v>13</v>
+      <c r="A87" t="s">
+        <v>4</v>
       </c>
       <c r="B87">
         <v>2021</v>
       </c>
       <c r="C87" t="s">
+        <v>26</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
         <v>5</v>
       </c>
-      <c r="D87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88">
-        <v>18</v>
-      </c>
       <c r="B88">
         <v>2021</v>
       </c>
       <c r="C88" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D88">
         <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89">
-        <v>18</v>
+      <c r="A89" t="s">
+        <v>5</v>
       </c>
       <c r="B89">
         <v>2021</v>
       </c>
       <c r="C89" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90">
-        <v>2</v>
+      <c r="A90" t="s">
+        <v>6</v>
       </c>
       <c r="B90">
         <v>2021</v>
       </c>
       <c r="C90" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D90">
         <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91">
-        <v>2</v>
+      <c r="A91" t="s">
+        <v>6</v>
       </c>
       <c r="B91">
         <v>2021</v>
       </c>
       <c r="C91" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92">
-        <v>9</v>
+      <c r="A92" t="s">
+        <v>7</v>
       </c>
       <c r="B92">
         <v>2021</v>
       </c>
       <c r="C92" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D92">
         <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93">
+      <c r="A93" t="s">
+        <v>7</v>
+      </c>
+      <c r="B93">
+        <v>2021</v>
+      </c>
+      <c r="C93" t="s">
+        <v>26</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
+        <v>8</v>
+      </c>
+      <c r="B94">
+        <v>2021</v>
+      </c>
+      <c r="C94" t="s">
+        <v>25</v>
+      </c>
+      <c r="D94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
+        <v>8</v>
+      </c>
+      <c r="B95">
+        <v>2021</v>
+      </c>
+      <c r="C95" t="s">
+        <v>26</v>
+      </c>
+      <c r="D95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
         <v>9</v>
       </c>
-      <c r="B93">
-        <v>2021</v>
-      </c>
-      <c r="C93" t="s">
-        <v>5</v>
-      </c>
-      <c r="D93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94">
+      <c r="B96">
+        <v>2021</v>
+      </c>
+      <c r="C96" t="s">
+        <v>25</v>
+      </c>
+      <c r="D96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
+        <v>9</v>
+      </c>
+      <c r="B97">
+        <v>2021</v>
+      </c>
+      <c r="C97" t="s">
+        <v>26</v>
+      </c>
+      <c r="D97">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
+        <v>10</v>
+      </c>
+      <c r="B98">
+        <v>2021</v>
+      </c>
+      <c r="C98" t="s">
+        <v>25</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
+        <v>10</v>
+      </c>
+      <c r="B99">
+        <v>2021</v>
+      </c>
+      <c r="C99" t="s">
+        <v>26</v>
+      </c>
+      <c r="D99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
+        <v>11</v>
+      </c>
+      <c r="B100">
+        <v>2021</v>
+      </c>
+      <c r="C100" t="s">
+        <v>25</v>
+      </c>
+      <c r="D100">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
+        <v>11</v>
+      </c>
+      <c r="B101">
+        <v>2021</v>
+      </c>
+      <c r="C101" t="s">
+        <v>26</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" t="s">
+        <v>12</v>
+      </c>
+      <c r="B102">
+        <v>2021</v>
+      </c>
+      <c r="C102" t="s">
+        <v>25</v>
+      </c>
+      <c r="D102">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" t="s">
+        <v>12</v>
+      </c>
+      <c r="B103">
+        <v>2021</v>
+      </c>
+      <c r="C103" t="s">
+        <v>26</v>
+      </c>
+      <c r="D103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" t="s">
+        <v>13</v>
+      </c>
+      <c r="B104">
+        <v>2021</v>
+      </c>
+      <c r="C104" t="s">
+        <v>25</v>
+      </c>
+      <c r="D104">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" t="s">
+        <v>13</v>
+      </c>
+      <c r="B105">
+        <v>2021</v>
+      </c>
+      <c r="C105" t="s">
+        <v>26</v>
+      </c>
+      <c r="D105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" t="s">
+        <v>14</v>
+      </c>
+      <c r="B106">
+        <v>2021</v>
+      </c>
+      <c r="C106" t="s">
+        <v>25</v>
+      </c>
+      <c r="D106">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" t="s">
+        <v>14</v>
+      </c>
+      <c r="B107">
+        <v>2021</v>
+      </c>
+      <c r="C107" t="s">
+        <v>26</v>
+      </c>
+      <c r="D107">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" t="s">
         <v>15</v>
       </c>
-      <c r="B94">
-        <v>2021</v>
-      </c>
-      <c r="C94" t="s">
-        <v>4</v>
-      </c>
-      <c r="D94">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95">
+      <c r="B108">
+        <v>2021</v>
+      </c>
+      <c r="C108" t="s">
+        <v>25</v>
+      </c>
+      <c r="D108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" t="s">
         <v>15</v>
       </c>
-      <c r="B95">
-        <v>2021</v>
-      </c>
-      <c r="C95" t="s">
-        <v>5</v>
-      </c>
-      <c r="D95">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96">
-        <v>20</v>
-      </c>
-      <c r="B96">
-        <v>2021</v>
-      </c>
-      <c r="C96" t="s">
-        <v>4</v>
-      </c>
-      <c r="D96">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97">
-        <v>20</v>
-      </c>
-      <c r="B97">
-        <v>2021</v>
-      </c>
-      <c r="C97" t="s">
-        <v>5</v>
-      </c>
-      <c r="D97">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98">
-        <v>6</v>
-      </c>
-      <c r="B98">
-        <v>2021</v>
-      </c>
-      <c r="C98" t="s">
-        <v>4</v>
-      </c>
-      <c r="D98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99">
-        <v>6</v>
-      </c>
-      <c r="B99">
-        <v>2021</v>
-      </c>
-      <c r="C99" t="s">
-        <v>5</v>
-      </c>
-      <c r="D99">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100">
-        <v>12</v>
-      </c>
-      <c r="B100">
-        <v>2021</v>
-      </c>
-      <c r="C100" t="s">
-        <v>4</v>
-      </c>
-      <c r="D100">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101">
-        <v>12</v>
-      </c>
-      <c r="B101">
-        <v>2021</v>
-      </c>
-      <c r="C101" t="s">
-        <v>5</v>
-      </c>
-      <c r="D101">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102">
+      <c r="B109">
+        <v>2021</v>
+      </c>
+      <c r="C109" t="s">
+        <v>26</v>
+      </c>
+      <c r="D109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
+        <v>16</v>
+      </c>
+      <c r="B110">
+        <v>2021</v>
+      </c>
+      <c r="C110" t="s">
+        <v>25</v>
+      </c>
+      <c r="D110">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" t="s">
+        <v>16</v>
+      </c>
+      <c r="B111">
+        <v>2021</v>
+      </c>
+      <c r="C111" t="s">
+        <v>26</v>
+      </c>
+      <c r="D111">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" t="s">
         <v>17</v>
       </c>
-      <c r="B102">
-        <v>2021</v>
-      </c>
-      <c r="C102" t="s">
-        <v>4</v>
-      </c>
-      <c r="D102">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103">
-        <v>17</v>
-      </c>
-      <c r="B103">
-        <v>2021</v>
-      </c>
-      <c r="C103" t="s">
-        <v>5</v>
-      </c>
-      <c r="D103">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104">
-        <v>8</v>
-      </c>
-      <c r="B104">
-        <v>2021</v>
-      </c>
-      <c r="C104" t="s">
-        <v>4</v>
-      </c>
-      <c r="D104">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105">
-        <v>8</v>
-      </c>
-      <c r="B105">
-        <v>2021</v>
-      </c>
-      <c r="C105" t="s">
-        <v>5</v>
-      </c>
-      <c r="D105">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106">
-        <v>3</v>
-      </c>
-      <c r="B106">
-        <v>2021</v>
-      </c>
-      <c r="C106" t="s">
-        <v>4</v>
-      </c>
-      <c r="D106">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107">
-        <v>3</v>
-      </c>
-      <c r="B107">
-        <v>2021</v>
-      </c>
-      <c r="C107" t="s">
-        <v>5</v>
-      </c>
-      <c r="D107">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108">
-        <v>16</v>
-      </c>
-      <c r="B108">
-        <v>2021</v>
-      </c>
-      <c r="C108" t="s">
-        <v>4</v>
-      </c>
-      <c r="D108">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109">
-        <v>16</v>
-      </c>
-      <c r="B109">
-        <v>2021</v>
-      </c>
-      <c r="C109" t="s">
-        <v>5</v>
-      </c>
-      <c r="D109">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110">
-        <v>11</v>
-      </c>
-      <c r="B110">
-        <v>2021</v>
-      </c>
-      <c r="C110" t="s">
-        <v>4</v>
-      </c>
-      <c r="D110">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111">
-        <v>11</v>
-      </c>
-      <c r="B111">
-        <v>2021</v>
-      </c>
-      <c r="C111" t="s">
-        <v>5</v>
-      </c>
-      <c r="D111">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112">
-        <v>10</v>
-      </c>
       <c r="B112">
         <v>2021</v>
       </c>
       <c r="C112" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D112">
         <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:4">
-      <c r="A113">
-        <v>10</v>
+      <c r="A113" t="s">
+        <v>17</v>
       </c>
       <c r="B113">
         <v>2021</v>
       </c>
       <c r="C113" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D113">
         <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:4">
-      <c r="A114">
-        <v>4</v>
+      <c r="A114" t="s">
+        <v>18</v>
       </c>
       <c r="B114">
         <v>2021</v>
       </c>
       <c r="C114" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D114">
         <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:4">
-      <c r="A115">
-        <v>4</v>
+      <c r="A115" t="s">
+        <v>18</v>
       </c>
       <c r="B115">
         <v>2021</v>
       </c>
       <c r="C115" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D115">
         <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:4">
-      <c r="A116">
+      <c r="A116" t="s">
         <v>19</v>
       </c>
       <c r="B116">
         <v>2021</v>
       </c>
       <c r="C116" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D116">
         <v>3</v>
       </c>
     </row>
     <row r="117" spans="1:4">
-      <c r="A117">
+      <c r="A117" t="s">
         <v>19</v>
       </c>
       <c r="B117">
         <v>2021</v>
       </c>
       <c r="C117" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D117">
         <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:4">
-      <c r="A118">
-        <v>14</v>
+      <c r="A118" t="s">
+        <v>20</v>
       </c>
       <c r="B118">
         <v>2021</v>
       </c>
       <c r="C118" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D118">
         <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:4">
-      <c r="A119">
-        <v>14</v>
+      <c r="A119" t="s">
+        <v>20</v>
       </c>
       <c r="B119">
         <v>2021</v>
       </c>
       <c r="C119" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D119">
         <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:4">
-      <c r="A120">
-        <v>1</v>
+      <c r="A120" t="s">
+        <v>21</v>
       </c>
       <c r="B120">
         <v>2021</v>
       </c>
       <c r="C120" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D120">
         <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:4">
-      <c r="A121">
-        <v>1</v>
+      <c r="A121" t="s">
+        <v>21</v>
       </c>
       <c r="B121">
         <v>2021</v>
       </c>
       <c r="C121" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D121">
         <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:4">
-      <c r="A122">
-        <v>7</v>
+      <c r="A122" t="s">
+        <v>22</v>
       </c>
       <c r="B122">
         <v>2021</v>
       </c>
       <c r="C122" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D122">
         <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:4">
-      <c r="A123">
-        <v>7</v>
+      <c r="A123" t="s">
+        <v>22</v>
       </c>
       <c r="B123">
         <v>2021</v>
       </c>
       <c r="C123" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D123">
         <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:4">
-      <c r="A124">
-        <v>21</v>
+      <c r="A124" t="s">
+        <v>23</v>
       </c>
       <c r="B124">
         <v>2021</v>
       </c>
       <c r="C124" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D124">
         <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:4">
-      <c r="A125">
-        <v>21</v>
+      <c r="A125" t="s">
+        <v>23</v>
       </c>
       <c r="B125">
         <v>2021</v>
       </c>
       <c r="C125" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D125">
         <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:4">
-      <c r="A126">
-        <v>5</v>
+      <c r="A126" t="s">
+        <v>24</v>
       </c>
       <c r="B126">
         <v>2021</v>
       </c>
       <c r="C126" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D126">
         <v>4</v>
       </c>
     </row>
     <row r="127" spans="1:4">
-      <c r="A127">
-        <v>5</v>
+      <c r="A127" t="s">
+        <v>24</v>
       </c>
       <c r="B127">
         <v>2021</v>
       </c>
       <c r="C127" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D127">
         <v>4</v>
